--- a/artfynd/A 44450-2024 artfynd.xlsx
+++ b/artfynd/A 44450-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120784182</v>
+        <v>120781513</v>
       </c>
       <c r="B2" t="n">
-        <v>90973</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421140</v>
+        <v>421136</v>
       </c>
       <c r="R2" t="n">
-        <v>6882757</v>
+        <v>6882724</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120782427</v>
+        <v>120783006</v>
       </c>
       <c r="B3" t="n">
-        <v>78598</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420856</v>
+        <v>420741</v>
       </c>
       <c r="R3" t="n">
-        <v>6882657</v>
+        <v>6882790</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120781348</v>
+        <v>120783211</v>
       </c>
       <c r="B4" t="n">
-        <v>91127</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>421132</v>
+        <v>420685</v>
       </c>
       <c r="R4" t="n">
-        <v>6882724</v>
+        <v>6882832</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120784229</v>
+        <v>120784182</v>
       </c>
       <c r="B5" t="n">
-        <v>90973</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,12 +986,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>421156</v>
+        <v>421140</v>
       </c>
       <c r="R5" t="n">
-        <v>6882794</v>
+        <v>6882757</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120782853</v>
+        <v>120784229</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>420743</v>
+        <v>421156</v>
       </c>
       <c r="R6" t="n">
-        <v>6882744</v>
+        <v>6882794</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120784230</v>
+        <v>120781617</v>
       </c>
       <c r="B7" t="n">
-        <v>90687</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>421156</v>
+        <v>421130</v>
       </c>
       <c r="R7" t="n">
-        <v>6882794</v>
+        <v>6882723</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120781617</v>
+        <v>120782365</v>
       </c>
       <c r="B8" t="n">
-        <v>90687</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>421130</v>
+        <v>420915</v>
       </c>
       <c r="R8" t="n">
-        <v>6882723</v>
+        <v>6882645</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120783151</v>
+        <v>120783000</v>
       </c>
       <c r="B9" t="n">
-        <v>90687</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>420717</v>
+        <v>420741</v>
       </c>
       <c r="R9" t="n">
-        <v>6882786</v>
+        <v>6882790</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120782516</v>
+        <v>120783151</v>
       </c>
       <c r="B10" t="n">
-        <v>78598</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>420803</v>
+        <v>420717</v>
       </c>
       <c r="R10" t="n">
-        <v>6882658</v>
+        <v>6882786</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1593,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120783000</v>
+        <v>120784230</v>
       </c>
       <c r="B11" t="n">
-        <v>90687</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>420741</v>
+        <v>421156</v>
       </c>
       <c r="R11" t="n">
-        <v>6882790</v>
+        <v>6882794</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1695,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120782365</v>
+        <v>120781348</v>
       </c>
       <c r="B12" t="n">
-        <v>90687</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>420915</v>
+        <v>421132</v>
       </c>
       <c r="R12" t="n">
-        <v>6882645</v>
+        <v>6882724</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1797,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120781513</v>
+        <v>120783611</v>
       </c>
       <c r="B13" t="n">
-        <v>90973</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>421136</v>
+        <v>420787</v>
       </c>
       <c r="R13" t="n">
-        <v>6882724</v>
+        <v>6882912</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1899,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120781273</v>
+        <v>120784226</v>
       </c>
       <c r="B14" t="n">
-        <v>78598</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>421151</v>
+        <v>421156</v>
       </c>
       <c r="R14" t="n">
-        <v>6882700</v>
+        <v>6882794</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2001,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120783611</v>
+        <v>120781273</v>
       </c>
       <c r="B15" t="n">
-        <v>91127</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>420787</v>
+        <v>421151</v>
       </c>
       <c r="R15" t="n">
-        <v>6882912</v>
+        <v>6882700</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2103,19 +2033,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120782965</v>
+        <v>120781397</v>
       </c>
       <c r="B16" t="n">
-        <v>78598</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2143,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>420741</v>
+        <v>421140</v>
       </c>
       <c r="R16" t="n">
-        <v>6882743</v>
+        <v>6882729</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2183,7 +2108,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Mycket allmän norr om stigen.</t>
+          <t>Allmän söder om stigen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2210,64 +2135,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120782894</v>
+        <v>120781819</v>
       </c>
       <c r="B17" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Österåsvallen, Österåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>420739</v>
+        <v>421129</v>
       </c>
       <c r="R17" t="n">
-        <v>6882740</v>
+        <v>6882724</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2326,19 +2232,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120781397</v>
+        <v>120781867</v>
       </c>
       <c r="B18" t="n">
-        <v>78598</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2366,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>421140</v>
+        <v>421085</v>
       </c>
       <c r="R18" t="n">
-        <v>6882729</v>
+        <v>6882666</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2402,11 +2303,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Allmän söder om stigen.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2433,19 +2329,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120781867</v>
+        <v>120782195</v>
       </c>
       <c r="B19" t="n">
-        <v>78598</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2473,13 +2364,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421085</v>
+        <v>420979</v>
       </c>
       <c r="R19" t="n">
-        <v>6882666</v>
+        <v>6882655</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2535,37 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120783211</v>
+        <v>120782427</v>
       </c>
       <c r="B20" t="n">
-        <v>90973</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2575,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>420685</v>
+        <v>420856</v>
       </c>
       <c r="R20" t="n">
-        <v>6882832</v>
+        <v>6882657</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2637,59 +2523,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120781901</v>
+        <v>120782516</v>
       </c>
       <c r="B21" t="n">
-        <v>57459</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Österåsvallen, Österåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421076</v>
+        <v>420803</v>
       </c>
       <c r="R21" t="n">
-        <v>6882671</v>
+        <v>6882658</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2748,19 +2620,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120781819</v>
+        <v>120782853</v>
       </c>
       <c r="B22" t="n">
-        <v>78598</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2788,13 +2655,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421129</v>
+        <v>420743</v>
       </c>
       <c r="R22" t="n">
-        <v>6882724</v>
+        <v>6882744</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2850,37 +2717,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120783006</v>
+        <v>120782965</v>
       </c>
       <c r="B23" t="n">
-        <v>90973</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2893,7 +2755,7 @@
         <v>420741</v>
       </c>
       <c r="R23" t="n">
-        <v>6882790</v>
+        <v>6882743</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2926,6 +2788,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Mycket allmän norr om stigen.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2952,37 +2819,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120784226</v>
+        <v>120783445</v>
       </c>
       <c r="B24" t="n">
-        <v>91127</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2992,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421156</v>
+        <v>420694</v>
       </c>
       <c r="R24" t="n">
-        <v>6882794</v>
+        <v>6883002</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3054,15 +2916,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120782195</v>
+        <v>120782894</v>
       </c>
       <c r="B25" t="n">
-        <v>78598</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3070,37 +2927,51 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Österåsvallen, Österåsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>420979</v>
+        <v>420739</v>
       </c>
       <c r="R25" t="n">
-        <v>6882655</v>
+        <v>6882740</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3153,6 +3024,209 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120783454</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Österåsvallen, Österåsvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>420694</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6883002</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Linsell</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120781901</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Österåsvallen, Österåsvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>421076</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6882671</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Linsell</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44450-2024 artfynd.xlsx
+++ b/artfynd/A 44450-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120781513</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120783006</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120783211</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120784182</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120784229</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120781617</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120782365</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120783000</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120783151</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120784230</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120781348</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120783611</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120784226</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120781273</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120781397</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2229,6 +2309,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120781819</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2326,6 +2411,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120781867</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2423,6 +2513,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120782195</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2520,6 +2615,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120782427</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2617,6 +2717,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120782516</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2714,6 +2819,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120782853</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2816,6 +2926,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120782965</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2913,6 +3028,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120783445</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3024,6 +3144,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120782894</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3121,6 +3246,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120783454</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3227,8 +3357,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120781901</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>